--- a/sim/resources/sample/ResearchInstitute.xlsx
+++ b/sim/resources/sample/ResearchInstitute.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="48">
   <si>
     <t>id</t>
   </si>
@@ -43,16 +43,13 @@
     <t>游戏名称</t>
   </si>
   <si>
-    <t>组别</t>
-  </si>
-  <si>
     <t>属性技能位置坐标</t>
   </si>
   <si>
     <t>int</t>
   </si>
   <si>
-    <t>Map&lt;int{_}int&gt;{|}</t>
+    <t>string</t>
   </si>
   <si>
     <t>level</t>
@@ -61,55 +58,121 @@
     <t>gameType</t>
   </si>
   <si>
-    <t>team</t>
-  </si>
-  <si>
     <t>location</t>
   </si>
   <si>
+    <t>client</t>
+  </si>
+  <si>
     <t>超级明星</t>
   </si>
   <si>
-    <t>0_0</t>
-  </si>
-  <si>
-    <t>0_1|1_1|2_1</t>
-  </si>
-  <si>
-    <t>0_2</t>
-  </si>
-  <si>
-    <t>0_3</t>
+    <t>10030001,0_0</t>
+  </si>
+  <si>
+    <t>10030002,0_1|10030003,1_1|10030004,2_1</t>
+  </si>
+  <si>
+    <t>10030005,0_2</t>
+  </si>
+  <si>
+    <t>10030006,0_3</t>
+  </si>
+  <si>
+    <t>10030007,0_3|10030008,1_3</t>
   </si>
   <si>
     <t>神马飞扬</t>
   </si>
   <si>
-    <t>0_1|1_1|2_1|3_1</t>
-  </si>
-  <si>
-    <t>0_2|1_2|2_2</t>
+    <t>10340001,0_0</t>
+  </si>
+  <si>
+    <t>10340002,0_1|10340003,1_1|10340004,2_1|10340005,3_1</t>
+  </si>
+  <si>
+    <t>10340006,0_2|10340007,1_2|10340008,2_2</t>
+  </si>
+  <si>
+    <t>10340009,0_3</t>
+  </si>
+  <si>
+    <t>10340010,0_4|10340011,1_4</t>
   </si>
   <si>
     <t>金蛇招财</t>
   </si>
   <si>
+    <t>10350001,0_0</t>
+  </si>
+  <si>
+    <t>10350002,0_1|10350003,1_1|10350004,2_1|10350005,3_1</t>
+  </si>
+  <si>
+    <t>10350006,0_2|10350007,1_2|10350008,2_2</t>
+  </si>
+  <si>
+    <t>10350009,0_3</t>
+  </si>
+  <si>
+    <t>10350010,0_4|10350011,1_4</t>
+  </si>
+  <si>
     <t>圣诞狂欢夜</t>
   </si>
   <si>
-    <t>0_2|1_2|2_2|3_2</t>
+    <t>10170001,0_0</t>
+  </si>
+  <si>
+    <t>10170002,0_1|10170003,1_1|10170004,2_1|10170005,3_1</t>
+  </si>
+  <si>
+    <t>10170006,0_2|1017007,1_2|10170008,2_2|10170009,3_2</t>
+  </si>
+  <si>
+    <t>10170010,0_3</t>
+  </si>
+  <si>
+    <t>10170011,0_4|10170011,1_4</t>
   </si>
   <si>
     <t>篮球巨星</t>
   </si>
   <si>
+    <t>10180001,0_0</t>
+  </si>
+  <si>
+    <t>10180002,0_1|10180003,1_1|10180004_1|10180005,3_1</t>
+  </si>
+  <si>
+    <t>10180006,0_2|10180007,1_2|10180008,2_2|10180009,3_2</t>
+  </si>
+  <si>
+    <t>10180010,0_3</t>
+  </si>
+  <si>
+    <t>10180011,0_4|10180011,1_4</t>
+  </si>
+  <si>
     <t>杰克船长</t>
   </si>
   <si>
-    <t>0_3|1_3|2_3</t>
-  </si>
-  <si>
-    <t>0_4</t>
+    <t>10210001,0_0</t>
+  </si>
+  <si>
+    <t>10210002,0_1|10210003,1_1|10210004,2_1|10210005,3_1</t>
+  </si>
+  <si>
+    <t>10210006,0_2|10210007,1_2|10210008,2_2|10210009,3_2</t>
+  </si>
+  <si>
+    <t>10210010,0_3|10210011,1_3|10210012,2_3</t>
+  </si>
+  <si>
+    <t>10210013,0_4</t>
+  </si>
+  <si>
+    <t>10210011,0_5|10210011,1_5</t>
   </si>
 </sst>
 </file>
@@ -746,16 +809,13 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -765,8 +825,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="58" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1082,575 +1142,595 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F29"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="5"/>
+  <dimension ref="A1:E35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="10.5" style="2" customWidth="1"/>
-    <col min="3" max="3" width="11.375" style="2" customWidth="1"/>
-    <col min="4" max="5" width="17.75" style="2" customWidth="1"/>
-    <col min="6" max="6" width="18.375" style="2" customWidth="1"/>
-    <col min="7" max="7" width="16.375" style="3" customWidth="1"/>
-    <col min="8" max="10" width="9" style="3"/>
-    <col min="11" max="11" width="25.75" style="3" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="3"/>
+    <col min="2" max="2" width="10.5" style="1" customWidth="1"/>
+    <col min="3" max="3" width="11.375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.75" style="1" customWidth="1"/>
+    <col min="5" max="5" width="22.625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16.375" style="2" customWidth="1"/>
+    <col min="7" max="9" width="9" style="2"/>
+    <col min="10" max="10" width="25.75" style="2" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>6</v>
+      <c r="B2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>5</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="2" t="s">
+    </row>
+    <row r="4" spans="1:5">
+      <c r="E4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="F4" s="6"/>
-    </row>
-    <row r="5" spans="1:6">
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" s="1">
         <v>1001</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="1">
         <v>1</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="1">
         <v>100300</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="2">
-        <v>1</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" s="1">
         <v>1002</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="1">
         <v>1</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="1">
         <v>100300</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" s="2">
-        <v>2</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+      <c r="D6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" s="1">
         <v>1003</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="1">
         <v>1</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="1">
         <v>100300</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E7" s="2">
-        <v>3</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+      <c r="D7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" s="1">
         <v>1004</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="1">
         <v>1</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="1">
         <v>100300</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" s="2">
-        <v>4</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+      <c r="D8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" s="1">
         <v>1005</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9" s="1">
         <v>1</v>
       </c>
-      <c r="C9" s="2">
-        <v>103400</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E9" s="2">
-        <v>1</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
+      <c r="C9" s="1">
+        <v>100300</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10" s="1">
         <v>1006</v>
       </c>
-      <c r="B10" s="2">
-        <v>1</v>
-      </c>
-      <c r="C10" s="2">
+      <c r="B10" s="1">
+        <v>2</v>
+      </c>
+      <c r="C10" s="1">
         <v>103400</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E10" s="2">
-        <v>2</v>
-      </c>
-      <c r="F10" s="4" t="s">
+      <c r="E10" s="3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:5">
       <c r="A11" s="1">
         <v>1007</v>
       </c>
-      <c r="B11" s="2">
-        <v>1</v>
-      </c>
-      <c r="C11" s="2">
+      <c r="B11" s="1">
+        <v>2</v>
+      </c>
+      <c r="C11" s="1">
         <v>103400</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E11" s="2">
-        <v>3</v>
-      </c>
-      <c r="F11" s="7" t="s">
+      <c r="E11" s="3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:5">
       <c r="A12" s="1">
         <v>1008</v>
       </c>
-      <c r="B12" s="2">
-        <v>1</v>
-      </c>
-      <c r="C12" s="2">
+      <c r="B12" s="1">
+        <v>2</v>
+      </c>
+      <c r="C12" s="1">
         <v>103400</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E12" s="2">
-        <v>4</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
+      <c r="E12" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
       <c r="A13" s="1">
         <v>1009</v>
       </c>
-      <c r="B13" s="2">
-        <v>1</v>
-      </c>
-      <c r="C13" s="2">
-        <v>103500</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E13" s="2">
-        <v>1</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
+      <c r="B13" s="1">
+        <v>2</v>
+      </c>
+      <c r="C13" s="1">
+        <v>103400</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
       <c r="A14" s="1">
         <v>1010</v>
       </c>
-      <c r="B14" s="2">
-        <v>1</v>
-      </c>
-      <c r="C14" s="2">
-        <v>103500</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="2">
+      <c r="B14" s="1">
         <v>2</v>
       </c>
-      <c r="F14" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
+      <c r="C14" s="1">
+        <v>103400</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
       <c r="A15" s="1">
         <v>1011</v>
       </c>
-      <c r="B15" s="2">
-        <v>1</v>
-      </c>
-      <c r="C15" s="2">
+      <c r="B15" s="1">
+        <v>2</v>
+      </c>
+      <c r="C15" s="1">
         <v>103500</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="2">
-        <v>3</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
+      <c r="D15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
       <c r="A16" s="1">
         <v>1012</v>
       </c>
-      <c r="B16" s="2">
-        <v>1</v>
-      </c>
-      <c r="C16" s="2">
+      <c r="B16" s="1">
+        <v>2</v>
+      </c>
+      <c r="C16" s="1">
         <v>103500</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="2">
-        <v>4</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
+      <c r="D16" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17" s="1">
         <v>1013</v>
       </c>
-      <c r="B17" s="2">
+      <c r="B17" s="1">
         <v>2</v>
       </c>
-      <c r="C17" s="2">
-        <v>101700</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E17" s="2">
-        <v>1</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
+      <c r="C17" s="1">
+        <v>103500</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18" s="1">
         <v>1014</v>
       </c>
-      <c r="B18" s="2">
+      <c r="B18" s="1">
         <v>2</v>
       </c>
-      <c r="C18" s="2">
-        <v>101701</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E18" s="2">
-        <v>2</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
+      <c r="C18" s="1">
+        <v>103500</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
       <c r="A19" s="1">
         <v>1015</v>
       </c>
-      <c r="B19" s="2">
-        <v>2</v>
-      </c>
-      <c r="C19" s="2">
-        <v>101702</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E19" s="2">
-        <v>3</v>
-      </c>
-      <c r="F19" s="7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
+      <c r="B19" s="1">
+        <v>1</v>
+      </c>
+      <c r="C19" s="1">
+        <v>103500</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
       <c r="A20" s="1">
         <v>1016</v>
       </c>
-      <c r="B20" s="2">
+      <c r="B20" s="1">
         <v>2</v>
       </c>
-      <c r="C20" s="2">
-        <v>101703</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E20" s="2">
-        <v>4</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
+      <c r="C20" s="1">
+        <v>101700</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
       <c r="A21" s="1">
         <v>1017</v>
       </c>
-      <c r="B21" s="2">
+      <c r="B21" s="1">
         <v>2</v>
       </c>
-      <c r="C21" s="2">
-        <v>101800</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E21" s="2">
-        <v>1</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
+      <c r="C21" s="1">
+        <v>101700</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
       <c r="A22" s="1">
         <v>1018</v>
       </c>
-      <c r="B22" s="2">
+      <c r="B22" s="1">
         <v>2</v>
       </c>
-      <c r="C22" s="2">
-        <v>101800</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E22" s="2">
-        <v>2</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
+      <c r="C22" s="1">
+        <v>101700</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
       <c r="A23" s="1">
         <v>1019</v>
       </c>
-      <c r="B23" s="2">
+      <c r="B23" s="1">
         <v>2</v>
       </c>
-      <c r="C23" s="2">
-        <v>101800</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E23" s="2">
-        <v>3</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
+      <c r="C23" s="1">
+        <v>101700</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
       <c r="A24" s="1">
         <v>1020</v>
       </c>
-      <c r="B24" s="2">
+      <c r="B24" s="1">
         <v>2</v>
       </c>
-      <c r="C24" s="2">
-        <v>101800</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E24" s="2">
-        <v>4</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
+      <c r="C24" s="1">
+        <v>101700</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
       <c r="A25" s="1">
         <v>1021</v>
       </c>
-      <c r="B25" s="2">
-        <v>2</v>
-      </c>
-      <c r="C25" s="2">
-        <v>102100</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E25" s="2">
-        <v>1</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
+      <c r="B25" s="1">
+        <v>3</v>
+      </c>
+      <c r="C25" s="1">
+        <v>101800</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
       <c r="A26" s="1">
         <v>1022</v>
       </c>
-      <c r="B26" s="2">
-        <v>2</v>
-      </c>
-      <c r="C26" s="2">
-        <v>102100</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E26" s="2">
-        <v>2</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
+      <c r="B26" s="1">
+        <v>3</v>
+      </c>
+      <c r="C26" s="1">
+        <v>101800</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
       <c r="A27" s="1">
         <v>1023</v>
       </c>
-      <c r="B27" s="2">
-        <v>2</v>
-      </c>
-      <c r="C27" s="2">
-        <v>102100</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E27" s="2">
+      <c r="B27" s="1">
         <v>3</v>
       </c>
-      <c r="F27" s="7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
+      <c r="C27" s="1">
+        <v>101800</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
       <c r="A28" s="1">
         <v>1024</v>
       </c>
-      <c r="B28" s="2">
-        <v>2</v>
-      </c>
-      <c r="C28" s="2">
-        <v>102100</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E28" s="2">
-        <v>4</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
+      <c r="B28" s="1">
+        <v>3</v>
+      </c>
+      <c r="C28" s="1">
+        <v>101800</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
       <c r="A29" s="1">
         <v>1025</v>
       </c>
-      <c r="B29" s="2">
-        <v>2</v>
-      </c>
-      <c r="C29" s="2">
+      <c r="B29" s="1">
+        <v>3</v>
+      </c>
+      <c r="C29" s="1">
+        <v>101800</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="1">
+        <v>1026</v>
+      </c>
+      <c r="B30" s="1">
+        <v>4</v>
+      </c>
+      <c r="C30" s="1">
         <v>102100</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E29" s="2">
-        <v>5</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>26</v>
+      <c r="D30" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="1">
+        <v>1027</v>
+      </c>
+      <c r="B31" s="1">
+        <v>4</v>
+      </c>
+      <c r="C31" s="1">
+        <v>102100</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="1">
+        <v>1028</v>
+      </c>
+      <c r="B32" s="1">
+        <v>4</v>
+      </c>
+      <c r="C32" s="1">
+        <v>102100</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="1">
+        <v>1029</v>
+      </c>
+      <c r="B33" s="1">
+        <v>4</v>
+      </c>
+      <c r="C33" s="1">
+        <v>102100</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="1">
+        <v>1030</v>
+      </c>
+      <c r="B34" s="1">
+        <v>4</v>
+      </c>
+      <c r="C34" s="1">
+        <v>102100</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="1">
+        <v>1031</v>
+      </c>
+      <c r="B35" s="1">
+        <v>4</v>
+      </c>
+      <c r="C35" s="1">
+        <v>102100</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
